--- a/datasets/Energy/Details of Dataset/Details of Datasets.xlsx
+++ b/datasets/Energy/Details of Dataset/Details of Datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HiWi\tabbank\datasets\Energy\Details of Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1F92F2-64E2-436C-A158-ADFDFFA998C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2534420C-D301-4998-8BAD-3C6673F0642E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EA6F8067-0B2C-427F-AF2F-C339AFBDD94F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="176">
   <si>
     <t>Link</t>
   </si>
@@ -357,6 +357,251 @@
   </si>
   <si>
     <t>energy_dataset.csv</t>
+  </si>
+  <si>
+    <t>Smart Grid Real-Time Load Monitoring Dataset</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/smart-grid-real-time-load-monitoring-dataset</t>
+  </si>
+  <si>
+    <t>Time-series data for energy management, forecasting, and fault detection.</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/smart-meter-electricity-consumption-dataset</t>
+  </si>
+  <si>
+    <t>Smart Meter Electricity Consumption Dataset</t>
+  </si>
+  <si>
+    <t>This dataset contains smart meter electricity consumption data enriched with weather conditions, historical consumption statistics, and anomaly labels for detecting unusual electricity usage patterns. It is designed for anomaly detection, predictive modeling, and energy consumption analysis using advanced machine learning techniques. Use Cases:
+Anomaly Detection: Identify fraudulent or unusual electricity consumption.
+Energy Efficiency Analysis: Understand consumption trends and optimize energy use.
+Predictive Modeling: Train AI models for forecasting electricity demand.
+Smart Grid Management: Improve grid stability and power distribution.
+This dataset is ideal for machine learning researchers, data scientists, and energy analysts developing predictive models for real-time anomaly detection and energy optimization.</t>
+  </si>
+  <si>
+    <t>smart_meter_data.csv</t>
+  </si>
+  <si>
+    <t>Delhi 5-Minute Electricity Demand for Forecasting</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/yug201/delhi-5-minute-electricity-demand-for-forecasting</t>
+  </si>
+  <si>
+    <t>This dataset provides a comprehensive record of electricity demand in Delhi, India, at 5-minute intervals, alongside key weather parameters. Covering the period from January 2021 to December 2024, the dataset is designed to facilitate forecasting models and analysis of energy demand patterns influenced by weather conditions.</t>
+  </si>
+  <si>
+    <t>39K</t>
+  </si>
+  <si>
+    <t>powerdemand_5min_2021_to_2024_with weather.csv</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/microgrid-pv-ev-charging-dataset</t>
+  </si>
+  <si>
+    <t>Microgrid PV-EV Charging Dataset</t>
+  </si>
+  <si>
+    <t>PV_EV_Charging_Dataset.csv</t>
+  </si>
+  <si>
+    <t>This dataset is designed for research and development in demand-side energy management for a microgrid-connected PV-EV charging system. It contains real-time data representing solar power generation, EV charging parameters, microgrid load, and energy efficiency optimization. Target Variable
+Energy_Efficiency – 1 (Efficient charging), 0 (Inefficient charging)</t>
+  </si>
+  <si>
+    <t>This dataset is designed for simulating power grid operations, fault detection, and optimization in grid management. The dataset includes synthetic data related to power grid systems, such as load profiles, voltage and frequency stability metrics, power flow between grid nodes, and fault detection information. It is intended for use in research related to power grid optimization, fault detection, and grid efficiency improvement through advanced methods, including quantum computing-based optimization models.</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/power-grid</t>
+  </si>
+  <si>
+    <t>Power-Grid</t>
+  </si>
+  <si>
+    <t>power_grid_dataset.csv</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/iot-enabled-smart-grid-dataset</t>
+  </si>
+  <si>
+    <t>IoT-Enabled Smart Grid Dataset</t>
+  </si>
+  <si>
+    <t>Description
+This dataset is designed for AI and ML-based energy efficiency optimization in IoT-enabled smart grids. It contains real-time and historical data on power consumption, voltage, current, grid frequency, reactive and active power, renewable energy generation, and environmental conditions. The dataset supports energy forecasting, load balancing, and anomaly detection using AI-driven predictive analytics.
+The target variable, Energy_Efficiency_Score, quantifies the overall efficiency of power usage based on consumption patterns, renewable energy integration, and demand response events. This dataset is valuable for research on smart grid optimization, sustainable energy management, and AI-driven IoT applications.</t>
+  </si>
+  <si>
+    <t>iiot_smart_grid_dataset.csv</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/ev-charging-grid-optimization-dataset</t>
+  </si>
+  <si>
+    <t>EV Charging Grid Optimization Dataset</t>
+  </si>
+  <si>
+    <t>The EV Charging Grid Optimization Dataset is designed to support research in AI-driven energy management for electric vehicle (EV) charging systems. This dataset captures real-time power grid parameters, charging session details, and AI-optimized charging predictions to minimize power losses and voltage fluctuations.</t>
+  </si>
+  <si>
+    <t>EV_Charging_Grid_Optimization_Categorical.csv</t>
+  </si>
+  <si>
+    <t>This dataset contains comprehensive hourly data from January 1, 2021, to May 31, 2024, for the California region. The data focuses on electric vehicle (EV) charging demand and renewable energy production, including solar and wind energy. The dataset is structured to support analysis and optimization of EV charging using intelligent forecasting methods for solar and renewable energy in uncertain environments. The integrated solar and wind energy data are taken from https://catalog.data.gov/dataset/.</t>
+  </si>
+  <si>
+    <t>EV Charging Station Data- California Region</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/datasetengineer/ev-charging-station-data-california-region</t>
+  </si>
+  <si>
+    <t>TimeSeries</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/hybrid-energy-storage-dataset/data</t>
+  </si>
+  <si>
+    <t>This dataset is designed for optimizing Hybrid Energy Storage Systems (HESS). It includes real-time and historical data on renewable energy sources, energy storage levels, power distribution, and efficiency classification.
+The dataset aims to enhance energy allocation, hydrogen utilization, and power loss reduction while ensuring stability in renewable energy integration. It is suitable for researchers and practitioners working on smart grids, energy management, and reinforcement learning-based optimization.</t>
+  </si>
+  <si>
+    <t>Hybrid Energy Storage Dataset</t>
+  </si>
+  <si>
+    <t>HESS_Dataset.csv</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/isuranga/load-forecasting-dataset</t>
+  </si>
+  <si>
+    <t>Load Forecasting Dataset</t>
+  </si>
+  <si>
+    <t>This dataset contains historical data used for forecasting the electrical load of the national grid in Sri Lanka. The data spans from January 2020 to May 2025, with 189888 records representing electrical consumption in 15-minute intervals. This dataset is designed for use in predictive modeling, specifically for applying machine learning techniques such as Recurrent Neural Networks (RNNs) for short-term load forecasting.</t>
+  </si>
+  <si>
+    <t>Panama Electricity Load Forecasting</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/pateljay731/panama-electricity-load-forecasting?select=train.csv</t>
+  </si>
+  <si>
+    <t>This is the famous time-series Load (MW) forecast</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/smart-grid-stability-and-reliability-dataset</t>
+  </si>
+  <si>
+    <t>Smart Grid Stability and Reliability Dataset</t>
+  </si>
+  <si>
+    <t>This dataset is designed to support the development of machine learning models for predicting the stability and reliability of smart grids. It includes synthetic data collected from various grid sensors, historical performance indicators, and external factors such as weather conditions and energy demand forecasts. The dataset is structured to facilitate research into early detection of grid disturbances, fault identification, and the optimization of smart grid operations.
+The dataset also provides labels for grid stability (binary: stable or unstable) and failure risk (categorical: low, medium, or high), making it ideal for training and evaluating predictive models aimed at ensuring grid reliability and preventing potential breakdowns.</t>
+  </si>
+  <si>
+    <t>smart_grid_stability_dataset.csv</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/programmer3/multi-source-renewable-energy-distribution-dataset</t>
+  </si>
+  <si>
+    <t>Multi-Source Renewable Energy Distribution Dataset</t>
+  </si>
+  <si>
+    <t>This dataset provides a real representation of a multi-source renewable energy microgrid. It integrates solar, wind, and hydro generation with factors such as weather conditions, energy storage, backup systems, demand, and grid stability. Target columns (forecasted solar, wind, load, and optimal distribution) are included to facilitate training and evaluation of machine learning and optimization models, such as the proposed Ladybug Beetle–Weighted Random Forest Regression (LB-Weighted RFR).</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/renewable-energy-optimized-interior-design-dataset</t>
+  </si>
+  <si>
+    <t>Renewable Energy-Optimized Interior Design Dataset</t>
+  </si>
+  <si>
+    <t>The Renewable Energy-Optimized Interior Design Dataset is a dataset designed to support research on integrating renewable energy technologies into interior design for rural homes. It includes various structural, environmental, and energy-related attributes to optimize spatial planning, thermal efficiency, and energy consumption using computational intelligence techniques.
+This dataset provides valuable insights into energy-efficient housing by considering factors such as solar exposure, ventilation efficiency, lighting optimization, and the strategic placement of passive heating and cooling elements. The target variable, Energy Efficiency Score, quantifies the overall sustainability and effectiveness of interior designs in rural homes.</t>
+  </si>
+  <si>
+    <t>renewable_energy_rural_home_dataset.csv</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/ziya07/personalized-energy-marketing-analytics-dataset</t>
+  </si>
+  <si>
+    <t>Personalized Energy Marketing Analytics Dataset</t>
+  </si>
+  <si>
+    <t>The SmartPowerML dataset is a user-level dataset designed to simulate the operation of a Power Marketing Management Platform (PMMP) enhanced by machine learning. It captures detailed information on users’ electricity consumption behaviors, demographics, pricing plans, and marketing engagement. The dataset supports use cases such as consumption forecasting, dynamic pricing strategy development, user segmentation, and targeted marketing in the energy sector.
+This dataset is ideal for researchers and developers looking to build or evaluate machine learning models in the fields of energy analytics, smart grid management, and personalized marketing.</t>
+  </si>
+  <si>
+    <t>power_marketing_dataset.csv</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/chayanroy3/customer-churn-analysis-dataset/data</t>
+  </si>
+  <si>
+    <t>Customer Churn Analysis Dataset</t>
+  </si>
+  <si>
+    <t>This dataset is derived from the BCG Gamma Customer Churn Simulation on Forage, designed to help analysts understand and predict customer attrition. It contains detailed customer behavioral data, transaction history, and engagement metrics, making it ideal for churn prediction models, exploratory data analysis (EDA), and machine learning applications.
+Potential Use Cases
+Predictive Modeling: Build machine learning models to classify churned vs. non-churned customers.
+Customer Segmentation: Identify high-risk customer groups.</t>
+  </si>
+  <si>
+    <t>client_data.csv</t>
+  </si>
+  <si>
+    <t>14K</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/gatabhjsbaj/powercos-customer-company-dataset/data</t>
+  </si>
+  <si>
+    <t>PowerCo's Customer DataSet</t>
+  </si>
+  <si>
+    <t>The Client Data dataset includes detailed information about clients and their energy consumption patterns. This data can be used to understand customer behavior and preferences, as well as to tailor services and offers. The Data for Predictions dataset is designed for building predictive models. It includes a variety of features that can be used to predict future consumption patterns, pricing, or other key metrics.</t>
+  </si>
+  <si>
+    <t>14K + 8K</t>
+  </si>
+  <si>
+    <t>26+64</t>
+  </si>
+  <si>
+    <t>client_data_PowerCo.csv
+data_for_predictions.csv</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/muhammadwaqas023/predictive-maintenance-oil-and-gas-pipeline-data</t>
+  </si>
+  <si>
+    <t>Predictive maintenance oil and gas pipeline data</t>
+  </si>
+  <si>
+    <t>This dataset contains 1,000 samples of pipeline data collected from the oil and gas industry, intended for use in predictive maintenance modeling. Each record represents sensor and operational data from pipelines, with corresponding labels indicating whether maintenance was required.
+The goal is to develop models that can predict potential failures or maintenance needs before they occur, ensuring pipeline safety, reducing downtime, and minimizing operational costs.</t>
+  </si>
+  <si>
+    <t>market_pipe_thickness_loss_dataset.csv</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/datasets/muhammadwaqas023/pipeline-dataset-in-oil-and-gas-sector</t>
+  </si>
+  <si>
+    <t>Pipeline dataset in oil and gas sector/fertilizer</t>
+  </si>
+  <si>
+    <t>This pipeline dataset used in different sector like oil and gas sector and fertilizers. This dataset is about 1000 pipeline dataset with different pipe size, materials, material grade, corrosion impact etc</t>
+  </si>
+  <si>
+    <t>pipe_thickness_loss_dataset.csv</t>
   </si>
 </sst>
 </file>
@@ -643,8 +888,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{21B586A9-3042-4314-8FAF-F47D783E7A62}" name="Table1" displayName="Table1" ref="A1:F20" totalsRowShown="0" headerRowDxfId="6">
-  <autoFilter ref="A1:F20" xr:uid="{21B586A9-3042-4314-8FAF-F47D783E7A62}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{21B586A9-3042-4314-8FAF-F47D783E7A62}" name="Table1" displayName="Table1" ref="A1:F39" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="A1:F39" xr:uid="{21B586A9-3042-4314-8FAF-F47D783E7A62}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{542FC159-17C1-48C5-BB73-EB852F8F121B}" name="Dataset Name" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{64F05B61-53CA-4D95-9696-533DFF04E22B}" name="File Name" dataDxfId="4"/>
@@ -954,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2CFAE7-9EA6-40E4-B9C4-733AE6062B4D}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.6640625" customWidth="1"/>
@@ -1286,42 +1531,42 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="144" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="1">
         <v>1000</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="1">
         <v>29</v>
       </c>
     </row>
@@ -1345,51 +1590,419 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="21" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="9">
+        <v>5000</v>
+      </c>
+      <c r="F21" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F24" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="9">
+        <v>8737</v>
+      </c>
+      <c r="F25" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E28" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" s="9">
+        <v>500</v>
+      </c>
+      <c r="F29" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F30" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F33" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F34" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+    </row>
+    <row r="36" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+    </row>
+    <row r="37" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+    </row>
+    <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>29</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C52" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>31</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C53" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>26</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C55" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>27</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C56" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>37</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C57" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>39</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C61" t="s">
         <v>40</v>
       </c>
     </row>

--- a/datasets/Energy/Details of Dataset/Details of Datasets.xlsx
+++ b/datasets/Energy/Details of Dataset/Details of Datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HiWi\tabbank\datasets\Energy\Details of Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2534420C-D301-4998-8BAD-3C6673F0642E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DF6950-24DA-4A5F-9BD0-D8DAB5BB9492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EA6F8067-0B2C-427F-AF2F-C339AFBDD94F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="176">
   <si>
     <t>Link</t>
   </si>
@@ -217,15 +217,9 @@
     <t>19K</t>
   </si>
   <si>
-    <t>energydata_complete.csv</t>
-  </si>
-  <si>
     <t>The dataset contains data points collected from a Combined Cycle Power Plant over 6 years (2006-2011), when the power plant was set to work with full load. Features consist of hourly average ambient variables Temperature, Ambient Pressure, Relative Humidity and Exhaust Vacuum to predict the net hourly electrical energy output of the plant.</t>
   </si>
   <si>
-    <t>Folds5x2_pp.xlsx</t>
-  </si>
-  <si>
     <t>GREEND is an energy dataset containing power measurements collected from multiple households in Austria and Italy. It provides detailed energy profiles on a per device basis with a sampling rate of 1 Hz.</t>
   </si>
   <si>
@@ -236,9 +230,6 @@
   </si>
   <si>
     <t>We perform energy analysis using 12 different building shapes simulated in Ecotect. The buildings differ with respect to the glazing area, the glazing area distribution, and the orientation, amongst other parameters. We simulate various settings as functions of the afore-mentioned characteristics to obtain 768 building shapes. The dataset comprises 768 samples and 8 features, aiming to predict two real valued responses. It can also be used as a multi-class classification problem if the response is rounded to the nearest integer.</t>
-  </si>
-  <si>
-    <t>ENB2012_data.xlsx</t>
   </si>
   <si>
     <t>The data is collected from a smart small-scale steel industry in South Korea. The information gathered is from the DAEWOO Steel Co. Ltd in Gwangyang, South Korea. It produces several types of coils, steel plates, and iron plates. The information on electricity consumption is held in a cloud-based system. The information on energy consumption of the industry is stored on the website of the Korea Electric Power Corporation (pccs.kepco.go.kr), and the perspectives on daily, monthly, and annual data are calculated and shown.</t>
@@ -269,10 +260,6 @@
   </si>
   <si>
     <t>The PIRvision dataset contains occupancy detection data collected from a Synchronized Low-Energy Electronically-chopped Passive Infra-Red sensing node in residential and office environments. Each observation represents 4 seconds of recorded human activity within the sensor Field-of-View (FoV).</t>
-  </si>
-  <si>
-    <t>pirvision_office_dataset1.csv
-pirvision_office_dataset2.csv</t>
   </si>
   <si>
     <t>55+55</t>
@@ -310,9 +297,6 @@
   </si>
   <si>
     <t>50K</t>
-  </si>
-  <si>
-    <t>T1.csv</t>
   </si>
   <si>
     <t>The dataset contains eight attributes (or features) and two responses (or outcomes). The aim is to use the eight features to predict each of the two responses.</t>
@@ -602,6 +586,21 @@
   </si>
   <si>
     <t>pipe_thickness_loss_dataset.csv</t>
+  </si>
+  <si>
+    <t>Appliances Energy Prediction.csv</t>
+  </si>
+  <si>
+    <t>Combined Cycle Power Plant.csv</t>
+  </si>
+  <si>
+    <t>Energy_Efficiency.csv</t>
+  </si>
+  <si>
+    <t>pirvision_office_dataset1.csv</t>
+  </si>
+  <si>
+    <t>Wind Turbine Scada Dataset.csv</t>
   </si>
 </sst>
 </file>
@@ -666,7 +665,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -687,12 +686,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1244,7 +1237,7 @@
         <v>52</v>
       </c>
       <c r="E2" s="1">
-        <v>8417</v>
+        <v>4209</v>
       </c>
       <c r="F2" s="1">
         <v>385</v>
@@ -1275,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>6</v>
@@ -1295,13 +1288,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="1">
         <v>9568</v>
@@ -1315,13 +1308,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -1331,13 +1324,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -1347,13 +1340,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>173</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E8" s="1">
         <v>768</v>
@@ -1367,16 +1360,16 @@
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1">
         <v>11</v>
@@ -1387,31 +1380,33 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1421,19 +1416,19 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
@@ -1441,13 +1436,13 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1">
         <v>1000</v>
@@ -1461,19 +1456,19 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -1481,7 +1476,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>36</v>
@@ -1495,16 +1490,16 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F16" s="1">
         <v>5</v>
@@ -1515,13 +1510,13 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E17" s="1">
         <v>768</v>
@@ -1532,16 +1527,16 @@
     </row>
     <row r="18" spans="1:6" ht="144" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E18" s="1">
         <v>1000</v>
@@ -1552,19 +1547,19 @@
     </row>
     <row r="19" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F19" s="1">
         <v>29</v>
@@ -1575,13 +1570,13 @@
         <v>46</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1">
         <v>3650</v>
@@ -1591,364 +1586,364 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F21" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="E22" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="9">
-        <v>5000</v>
-      </c>
-      <c r="F21" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="F22" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="D23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F22" s="9">
+      <c r="E24" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F24" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="1">
+        <v>8737</v>
+      </c>
+      <c r="F25" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="1">
+        <v>500</v>
+      </c>
+      <c r="F29" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F30" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" s="9">
+    <row r="31" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F31" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="1">
         <v>1000</v>
       </c>
-      <c r="F23" s="9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E24" s="9">
+      <c r="F33" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E34" s="1">
         <v>1000</v>
       </c>
-      <c r="F24" s="9">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="8" t="s">
+      <c r="F34" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" s="9">
-        <v>8737</v>
-      </c>
-      <c r="F25" s="9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E26" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F26" s="9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="144" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F27" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="E28" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F28" s="9">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" s="9">
-        <v>500</v>
-      </c>
-      <c r="F29" s="9">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="E30" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F30" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F31" s="9">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F33" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F34" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-    </row>
-    <row r="36" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-    </row>
-    <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>131</v>
-      </c>
       <c r="C39" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
+        <v>96</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
@@ -2025,10 +2020,27 @@
     <hyperlink ref="C16" r:id="rId15" xr:uid="{C267BDF6-6DAA-4BA2-851A-D9DCD6829A3B}"/>
     <hyperlink ref="C17" r:id="rId16" xr:uid="{206B57A0-34C2-4D8E-A198-41735B03C771}"/>
     <hyperlink ref="C20" r:id="rId17" xr:uid="{0C83C8B7-B7B9-4FC9-8E4A-D3C6BD85EBF2}"/>
+    <hyperlink ref="C18" r:id="rId18" xr:uid="{406120BB-3953-43D0-9FD4-CD61DDBE00A7}"/>
+    <hyperlink ref="C19" r:id="rId19" xr:uid="{FB5FDC9C-2780-497C-B1D1-1385EBF112D8}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{0311E65D-2F20-41D8-AB87-9DCA08DAC63F}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{3E135099-BBA6-42A3-B0E2-EAB4653A5B3B}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{B5C4FE78-8C3B-42E4-BB0A-B6C7A824CD7B}"/>
+    <hyperlink ref="C24" r:id="rId23" xr:uid="{ADDD48DB-1A1F-41AF-9F08-F298574E3161}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{40B78C8C-5C0C-4AEC-9C7E-45477880B5CF}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{3F35CD5E-E8BC-4AD9-87A6-113BB4698015}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{85318783-700A-41E2-8B9B-8EE2D6E24C00}"/>
+    <hyperlink ref="C28" r:id="rId27" xr:uid="{263689D5-10A0-4199-BD14-A9632C6C37E6}"/>
+    <hyperlink ref="C29" r:id="rId28" xr:uid="{8F916FEB-9215-47AD-9BD0-B452051B88F6}"/>
+    <hyperlink ref="C30" r:id="rId29" xr:uid="{077FA9E7-B9E8-49AE-8276-62E8D4B2B82B}"/>
+    <hyperlink ref="C31" r:id="rId30" xr:uid="{0F02953C-A048-49F4-9577-5BE5BAB64BE8}"/>
+    <hyperlink ref="C32" r:id="rId31" xr:uid="{E2C8A966-A4C5-43C6-8FD6-212AFFC4222D}"/>
+    <hyperlink ref="C33" r:id="rId32" xr:uid="{1DA53EFB-A95C-4836-8F10-FC816ACD8D3D}"/>
+    <hyperlink ref="C34" r:id="rId33" xr:uid="{8CC3C032-73DE-40EC-89D9-2ACD4B097BCF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId34"/>
   <tableParts count="1">
-    <tablePart r:id="rId18"/>
+    <tablePart r:id="rId35"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datasets/Energy/Details of Dataset/Details of Datasets.xlsx
+++ b/datasets/Energy/Details of Dataset/Details of Datasets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HiWi\tabbank\datasets\Energy\Details of Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DF6950-24DA-4A5F-9BD0-D8DAB5BB9492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A7B3E8-EA06-48FB-8278-3F024B2F008D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EA6F8067-0B2C-427F-AF2F-C339AFBDD94F}"/>
   </bookViews>
@@ -644,12 +644,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -665,7 +671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -686,6 +692,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1256,7 +1265,7 @@
       <c r="D3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="8" t="s">
         <v>56</v>
       </c>
       <c r="F3" s="1">
@@ -1276,7 +1285,7 @@
       <c r="D4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="8" t="s">
         <v>58</v>
       </c>
       <c r="F4" s="1">
@@ -1368,7 +1377,7 @@
       <c r="D9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="8" t="s">
         <v>65</v>
       </c>
       <c r="F9" s="1">
@@ -1388,7 +1397,7 @@
       <c r="D10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="8" t="s">
         <v>70</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1424,7 +1433,7 @@
       <c r="D12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="8" t="s">
         <v>74</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1464,7 +1473,7 @@
       <c r="D14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="8" t="s">
         <v>79</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1498,7 +1507,7 @@
       <c r="D16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="8" t="s">
         <v>82</v>
       </c>
       <c r="F16" s="1">
@@ -1558,7 +1567,7 @@
       <c r="D19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="8" t="s">
         <v>65</v>
       </c>
       <c r="F19" s="1">
@@ -1618,7 +1627,7 @@
       <c r="D22" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="8" t="s">
         <v>105</v>
       </c>
       <c r="F22" s="1">
@@ -1798,7 +1807,7 @@
       <c r="D31" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="8" t="s">
         <v>156</v>
       </c>
       <c r="F31" s="1">
@@ -1818,7 +1827,7 @@
       <c r="D32" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="8" t="s">
         <v>160</v>
       </c>
       <c r="F32" s="1" t="s">
